--- a/成果物/松藤華奈様_コミッション計算_FY26.xlsx
+++ b/成果物/松藤華奈様_コミッション計算_FY26.xlsx
@@ -4475,7 +4475,7 @@
         </is>
       </c>
       <c r="B4" s="67" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="C4" s="68">
         <f>B4*(1-年間サマリー!$B$29)</f>
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="B8" s="70" t="n">
-        <v>19100</v>
+        <v>18600</v>
       </c>
       <c r="C8" s="68">
         <f>B8</f>
@@ -4648,9 +4648,9 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>※7月〜新料率(自己60/指名なし40/指名50/店販オプ5%・交通費なし)。指名料は売上から除外。</t>
+      <c r="A18" s="39" t="inlineStr">
+        <is>
+          <t>※7月〜新料率(自己60/指名なし40/指名50/店販オプ5%・交通費なし)。指名料は売上除外。フジイユメカの¥500は自己顧客(60%)扱い。</t>
         </is>
       </c>
     </row>
